--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0645B141-A789-4751-B35F-CBE6EE8CDF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AAFB6C-9865-4811-90A6-D33C69D47F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,6 +448,10 @@
   </si>
   <si>
     <t>玩家3普攻-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物韧性被打空对自己释放易伤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -844,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -1170,28 +1174,28 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="A24" s="1">
+        <v>25010001</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
@@ -1199,13 +1203,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>15</v>
+        <v>127</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -1213,13 +1217,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -1227,13 +1231,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>128</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -1241,13 +1245,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
@@ -1255,10 +1259,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>20001</v>
+        <v>10302</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1269,10 +1273,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -1283,10 +1287,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>4000001</v>
+        <v>30001</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1297,38 +1301,38 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>5000001</v>
+        <v>4000001</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
       </c>
       <c r="D33" s="2">
-        <v>31000010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>6000001</v>
+        <v>5000001</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
       </c>
       <c r="D34" s="2">
-        <v>31000020</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>6010001</v>
+        <v>6000001</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -1339,24 +1343,24 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>7000001</v>
+        <v>6010001</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>31000040</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>7010001</v>
+        <v>7000001</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -1367,24 +1371,24 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>8000001</v>
+        <v>7010001</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>31000030</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>8010001</v>
+        <v>8000001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -1395,24 +1399,24 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>9000001</v>
+        <v>8010001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
       </c>
       <c r="D40" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>10010001</v>
+        <v>9000001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1423,10 +1427,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>10020001</v>
+        <v>10010001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1437,10 +1441,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>11010001</v>
+        <v>10020001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -1451,10 +1455,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>54010001</v>
+        <v>11010001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -1465,10 +1469,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>54030001</v>
+        <v>54010001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1479,10 +1483,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>54050001</v>
+        <v>54030001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -1493,10 +1497,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>54070001</v>
+        <v>54050001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1507,10 +1511,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>54090001</v>
+        <v>54070001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1521,10 +1525,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>54110001</v>
+        <v>54090001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1535,10 +1539,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>54130001</v>
+        <v>54110001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1549,10 +1553,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>54150001</v>
+        <v>54130001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1563,10 +1567,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>54170001</v>
+        <v>54150001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1577,10 +1581,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>54190001</v>
+        <v>54170001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1591,10 +1595,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>54210001</v>
+        <v>54190001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1605,10 +1609,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>54230001</v>
+        <v>54210001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1619,10 +1623,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>54250001</v>
+        <v>54230001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1633,10 +1637,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>55010001</v>
+        <v>54250001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1647,10 +1651,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>55020001</v>
+        <v>55010001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1661,10 +1665,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>55030001</v>
+        <v>55020001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1675,10 +1679,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>55040001</v>
+        <v>55030001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1689,10 +1693,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>55050001</v>
+        <v>55040001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1703,10 +1707,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>55060001</v>
+        <v>55050001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1717,10 +1721,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>55070001</v>
+        <v>55060001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1731,10 +1735,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>56010001</v>
+        <v>55070001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1745,10 +1749,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>56040001</v>
+        <v>56010001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1759,10 +1763,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1773,10 +1777,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>56080001</v>
+        <v>56060001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1787,10 +1791,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>56100001</v>
+        <v>56080001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1801,10 +1805,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>57010001</v>
+        <v>56100001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1815,10 +1819,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>57040001</v>
+        <v>57010001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1829,10 +1833,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1843,10 +1847,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>57080001</v>
+        <v>57060001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1857,10 +1861,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>57100001</v>
+        <v>57080001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1871,10 +1875,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>57120001</v>
+        <v>57100001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1885,10 +1889,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>58010001</v>
+        <v>57120001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1899,10 +1903,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>58040001</v>
+        <v>58010001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1913,10 +1917,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>58060001</v>
+        <v>58040001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1927,10 +1931,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>58080001</v>
+        <v>58060001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1941,10 +1945,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>58110001</v>
+        <v>58080001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1955,10 +1959,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>59010001</v>
+        <v>58110001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -1969,10 +1973,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>59030001</v>
+        <v>59010001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -1983,10 +1987,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -1997,10 +2001,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2011,10 +2015,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2025,10 +2029,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2039,10 +2043,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>59130001</v>
+        <v>59110001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2053,10 +2057,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>59150001</v>
+        <v>59130001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2067,10 +2071,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>59180001</v>
+        <v>59150001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2081,10 +2085,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>59200001</v>
+        <v>59180001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2095,10 +2099,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>59220001</v>
+        <v>59200001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2109,10 +2113,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>60010001</v>
+        <v>59220001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2123,10 +2127,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2137,10 +2141,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2151,10 +2155,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2165,10 +2169,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2179,10 +2183,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>61020001</v>
+        <v>60110001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2193,10 +2197,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2207,10 +2211,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2221,10 +2225,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2235,10 +2239,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2249,10 +2253,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2263,10 +2267,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2277,10 +2281,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2291,22 +2295,36 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
+        <v>61160001</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C104" s="2">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="2">
         <v>61180001</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B105" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C104" s="2">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2">
+      <c r="C105" s="2">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D82" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:D29">
-    <sortCondition ref="A24:A29"/>
+  <autoFilter ref="A4:D83" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:D30">
+    <sortCondition ref="A25:A30"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AAFB6C-9865-4811-90A6-D33C69D47F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675CF6B9-4BCB-4B1E-A0D1-E59075E23A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,18 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>30010101,30010102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30020101,30020102,30020103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30030101,30030102,30030103,30030104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>INT_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -452,6 +440,10 @@
   </si>
   <si>
     <t>怪物韧性被打空对自己释放易伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100201011,100201021</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -557,7 +549,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -567,6 +559,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -870,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -904,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -912,7 +905,7 @@
         <v>5010001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -926,7 +919,7 @@
         <v>5020001</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -940,7 +933,7 @@
         <v>5030001</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -954,7 +947,7 @@
         <v>20010001</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1">
         <v>990102</v>
@@ -968,10 +961,10 @@
         <v>20020001</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -982,10 +975,10 @@
         <v>20030001</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -996,10 +989,10 @@
         <v>20040001</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1010,10 +1003,10 @@
         <v>20050001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -1024,10 +1017,10 @@
         <v>20060001</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -1038,10 +1031,10 @@
         <v>20070001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1052,10 +1045,10 @@
         <v>20080001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -1066,10 +1059,10 @@
         <v>20090001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1080,10 +1073,10 @@
         <v>20100001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1094,10 +1087,10 @@
         <v>20110001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1108,10 +1101,10 @@
         <v>20120001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1122,10 +1115,10 @@
         <v>20130001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1136,10 +1129,10 @@
         <v>20140001</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1150,10 +1143,10 @@
         <v>20150001</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1164,10 +1157,10 @@
         <v>20160001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1178,7 +1171,7 @@
         <v>25010001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -1194,8 +1187,8 @@
       <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>14</v>
+      <c r="C25" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
@@ -1206,7 +1199,7 @@
         <v>10102</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -1222,8 +1215,8 @@
       <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>15</v>
+      <c r="C27" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -1234,7 +1227,7 @@
         <v>10202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -1250,8 +1243,8 @@
       <c r="B29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>16</v>
+      <c r="C29" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
@@ -1262,7 +1255,7 @@
         <v>10302</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1290,7 +1283,7 @@
         <v>30001</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1304,7 +1297,7 @@
         <v>4000001</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -1318,7 +1311,7 @@
         <v>5000001</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -1332,7 +1325,7 @@
         <v>6000001</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -1346,7 +1339,7 @@
         <v>6010001</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -1360,7 +1353,7 @@
         <v>7000001</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -1374,7 +1367,7 @@
         <v>7010001</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -1388,7 +1381,7 @@
         <v>8000001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -1402,7 +1395,7 @@
         <v>8010001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -1416,7 +1409,7 @@
         <v>9000001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1430,7 +1423,7 @@
         <v>10010001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1444,7 +1437,7 @@
         <v>10020001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -1458,7 +1451,7 @@
         <v>11010001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -1472,7 +1465,7 @@
         <v>54010001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1486,7 +1479,7 @@
         <v>54030001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -1500,7 +1493,7 @@
         <v>54050001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1514,7 +1507,7 @@
         <v>54070001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1528,7 +1521,7 @@
         <v>54090001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1542,7 +1535,7 @@
         <v>54110001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1556,7 +1549,7 @@
         <v>54130001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1570,7 +1563,7 @@
         <v>54150001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1584,7 +1577,7 @@
         <v>54170001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1598,7 +1591,7 @@
         <v>54190001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1612,7 +1605,7 @@
         <v>54210001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1626,7 +1619,7 @@
         <v>54230001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1640,7 +1633,7 @@
         <v>54250001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1654,7 +1647,7 @@
         <v>55010001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1668,7 +1661,7 @@
         <v>55020001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1682,7 +1675,7 @@
         <v>55030001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1696,7 +1689,7 @@
         <v>55040001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1710,7 +1703,7 @@
         <v>55050001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1724,7 +1717,7 @@
         <v>55060001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1738,7 +1731,7 @@
         <v>55070001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1752,7 +1745,7 @@
         <v>56010001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1766,7 +1759,7 @@
         <v>56040001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1780,7 +1773,7 @@
         <v>56060001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1794,7 +1787,7 @@
         <v>56080001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1808,7 +1801,7 @@
         <v>56100001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1822,7 +1815,7 @@
         <v>57010001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1836,7 +1829,7 @@
         <v>57040001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1850,7 +1843,7 @@
         <v>57060001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1864,7 +1857,7 @@
         <v>57080001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1878,7 +1871,7 @@
         <v>57100001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1892,7 +1885,7 @@
         <v>57120001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1906,7 +1899,7 @@
         <v>58010001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1920,7 +1913,7 @@
         <v>58040001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1934,7 +1927,7 @@
         <v>58060001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1948,7 +1941,7 @@
         <v>58080001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1962,7 +1955,7 @@
         <v>58110001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -1976,7 +1969,7 @@
         <v>59010001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -1990,7 +1983,7 @@
         <v>59030001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -2004,7 +1997,7 @@
         <v>59050001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2018,7 +2011,7 @@
         <v>59070001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2032,7 +2025,7 @@
         <v>59090001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2046,7 +2039,7 @@
         <v>59110001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2060,7 +2053,7 @@
         <v>59130001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2074,7 +2067,7 @@
         <v>59150001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2088,7 +2081,7 @@
         <v>59180001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2102,7 +2095,7 @@
         <v>59200001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2116,7 +2109,7 @@
         <v>59220001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2130,7 +2123,7 @@
         <v>60010001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2144,7 +2137,7 @@
         <v>60030001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2158,7 +2151,7 @@
         <v>60060001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2172,7 +2165,7 @@
         <v>60090001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2186,7 +2179,7 @@
         <v>60110001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2200,7 +2193,7 @@
         <v>61020001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2214,7 +2207,7 @@
         <v>61040001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2228,7 +2221,7 @@
         <v>61060001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2242,7 +2235,7 @@
         <v>61080001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2256,7 +2249,7 @@
         <v>61100001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2270,7 +2263,7 @@
         <v>61120001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2284,7 +2277,7 @@
         <v>61140001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2298,7 +2291,7 @@
         <v>61160001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2312,7 +2305,7 @@
         <v>61180001</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C105" s="2">
         <v>0</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675CF6B9-4BCB-4B1E-A0D1-E59075E23A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3173971D-AF10-4D40-BABA-40C9611430C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$89</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -205,253 +205,315 @@
     <t>boss_03-普攻</t>
   </si>
   <si>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+  </si>
+  <si>
+    <t>闪电链</t>
+  </si>
+  <si>
+    <t>电磁爆炸</t>
+  </si>
+  <si>
+    <t>中毒传染</t>
+  </si>
+  <si>
+    <t>瘟疫传染</t>
+  </si>
+  <si>
+    <t>复活</t>
+  </si>
+  <si>
+    <t>生命药剂</t>
+  </si>
+  <si>
+    <t>击中回血</t>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+  </si>
+  <si>
+    <t>旋风斩</t>
+  </si>
+  <si>
+    <t>半月斩</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>攻击速度提高</t>
+  </si>
+  <si>
+    <t>攻击提高</t>
+  </si>
+  <si>
+    <t>防御提高</t>
+  </si>
+  <si>
+    <t>生命提高</t>
+  </si>
+  <si>
+    <t>击中回血效果提高</t>
+  </si>
+  <si>
+    <t>暴击几率提高</t>
+  </si>
+  <si>
+    <t>暴击伤害提高</t>
+  </si>
+  <si>
+    <t>伤害提高</t>
+  </si>
+  <si>
+    <t>受到伤害提高</t>
+  </si>
+  <si>
+    <t>持续伤害提高</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高</t>
+  </si>
+  <si>
+    <t>移动速度提高</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+  </si>
+  <si>
+    <t>攻击几率使目标冰冻</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放冰霜新星</t>
+  </si>
+  <si>
+    <t>冰霜新星触发释放冰霜新星</t>
+  </si>
+  <si>
+    <t>使冰冻目标再次冰冻时触发额外伤害</t>
+  </si>
+  <si>
+    <t>使目标冰冻时造成额外伤害</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰霜新星必定使目标冰冻</t>
+  </si>
+  <si>
+    <t>攻击几率使目标燃烧</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放陨石</t>
+  </si>
+  <si>
+    <t>燃烧造成的伤害提高</t>
+  </si>
+  <si>
+    <t>陨石必定使目标燃烧</t>
+  </si>
+  <si>
+    <t>击杀燃烧怪物时触发释放死亡爆炸</t>
+  </si>
+  <si>
+    <t>攻击几率使目标触电</t>
+  </si>
+  <si>
+    <t>闪电链可弹射</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放闪电链</t>
+  </si>
+  <si>
+    <t>提高触电时受到攻击造成的额外伤害</t>
+  </si>
+  <si>
+    <t>造成触电时立刻触发触电伤害</t>
+  </si>
+  <si>
+    <t>击杀触电怪时触发释放电磁爆炸</t>
+  </si>
+  <si>
+    <t>攻击几率使目标中毒</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放传染</t>
+  </si>
+  <si>
+    <t>使中毒目标再次中毒时造成额外伤害</t>
+  </si>
+  <si>
+    <t>击杀中毒怪物时触发释放瘟疫</t>
+  </si>
+  <si>
+    <t>使目标获得瘟疫状态</t>
+  </si>
+  <si>
+    <t>每损失指定比例血量触发获得护盾</t>
+  </si>
+  <si>
+    <t>护盾值-根据自身生命最大值比例</t>
+  </si>
+  <si>
+    <t>拥有护盾时同时有受伤降低效果</t>
+  </si>
+  <si>
+    <t>击杀怪物触发击杀回血效果</t>
+  </si>
+  <si>
+    <t>击杀回血-回复量根据击中回血数值倍率</t>
+  </si>
+  <si>
+    <t>满血触发效果</t>
+  </si>
+  <si>
+    <t>低血时同时有受到伤害降低效果</t>
+  </si>
+  <si>
+    <t>死亡时触发释放复活</t>
+  </si>
+  <si>
+    <t>复活时回复血郞、触发间隔、每轮挑战最大次数</t>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放多重打击</t>
+  </si>
+  <si>
+    <t>提高多重打击的额外伤害</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放旋风斩</t>
+  </si>
+  <si>
+    <t>释放旋风斩触发释放半月斩</t>
+  </si>
+  <si>
+    <t>光环技能-自身效果：光环范围提高-范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
+  </si>
+  <si>
+    <t>攻击次数触发技能重击</t>
+  </si>
+  <si>
+    <t>重击技能暴击率提高</t>
+  </si>
+  <si>
+    <t>暴击触发技能：暴击伤害提高、重击需要的攻击次数累计值+1，致命暴击状态</t>
+  </si>
+  <si>
+    <t>技能攻击累计额外次数</t>
+  </si>
+  <si>
+    <t>致命暴击状态触发技能攻击速度提高</t>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+  </si>
+  <si>
+    <t>斩杀时暴击触发斩杀血线变化</t>
+  </si>
+  <si>
+    <t>斩杀血线的值增加</t>
+  </si>
+  <si>
+    <t>玩家1档普攻-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家2档普攻-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家3普攻-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物韧性被打空对自己释放易伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>boss_05-普攻</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
-    <t>死亡爆炸</t>
-  </si>
-  <si>
-    <t>闪电链</t>
-  </si>
-  <si>
-    <t>电磁爆炸</t>
-  </si>
-  <si>
-    <t>中毒传染</t>
-  </si>
-  <si>
-    <t>瘟疫传染</t>
-  </si>
-  <si>
-    <t>复活</t>
-  </si>
-  <si>
-    <t>生命药剂</t>
-  </si>
-  <si>
-    <t>击中回血</t>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-  </si>
-  <si>
-    <t>旋风斩</t>
-  </si>
-  <si>
-    <t>半月斩</t>
-  </si>
-  <si>
-    <t>重击</t>
-  </si>
-  <si>
-    <t>攻击速度提高</t>
-  </si>
-  <si>
-    <t>攻击提高</t>
-  </si>
-  <si>
-    <t>防御提高</t>
-  </si>
-  <si>
-    <t>生命提高</t>
-  </si>
-  <si>
-    <t>击中回血效果提高</t>
-  </si>
-  <si>
-    <t>暴击几率提高</t>
-  </si>
-  <si>
-    <t>暴击伤害提高</t>
-  </si>
-  <si>
-    <t>伤害提高</t>
-  </si>
-  <si>
-    <t>受到伤害提高</t>
-  </si>
-  <si>
-    <t>持续伤害提高</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高</t>
-  </si>
-  <si>
-    <t>移动速度提高</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-  </si>
-  <si>
-    <t>攻击几率使目标冰冻</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放冰霜新星</t>
-  </si>
-  <si>
-    <t>冰霜新星触发释放冰霜新星</t>
-  </si>
-  <si>
-    <t>使冰冻目标再次冰冻时触发额外伤害</t>
-  </si>
-  <si>
-    <t>使目标冰冻时造成额外伤害</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰霜新星必定使目标冰冻</t>
-  </si>
-  <si>
-    <t>攻击几率使目标燃烧</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放陨石</t>
-  </si>
-  <si>
-    <t>燃烧造成的伤害提高</t>
-  </si>
-  <si>
-    <t>陨石必定使目标燃烧</t>
-  </si>
-  <si>
-    <t>击杀燃烧怪物时触发释放死亡爆炸</t>
-  </si>
-  <si>
-    <t>攻击几率使目标触电</t>
-  </si>
-  <si>
-    <t>闪电链可弹射</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放闪电链</t>
-  </si>
-  <si>
-    <t>提高触电时受到攻击造成的额外伤害</t>
-  </si>
-  <si>
-    <t>造成触电时立刻触发触电伤害</t>
-  </si>
-  <si>
-    <t>击杀触电怪时触发释放电磁爆炸</t>
-  </si>
-  <si>
-    <t>攻击几率使目标中毒</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放传染</t>
-  </si>
-  <si>
-    <t>使中毒目标再次中毒时造成额外伤害</t>
-  </si>
-  <si>
-    <t>击杀中毒怪物时触发释放瘟疫</t>
-  </si>
-  <si>
-    <t>使目标获得瘟疫状态</t>
-  </si>
-  <si>
-    <t>每损失指定比例血量触发获得护盾</t>
-  </si>
-  <si>
-    <t>护盾值-根据自身生命最大值比例</t>
-  </si>
-  <si>
-    <t>拥有护盾时同时有受伤降低效果</t>
-  </si>
-  <si>
-    <t>击杀怪物触发击杀回血效果</t>
-  </si>
-  <si>
-    <t>击杀回血-回复量根据击中回血数值倍率</t>
-  </si>
-  <si>
-    <t>满血触发效果</t>
-  </si>
-  <si>
-    <t>低血时同时有受到伤害降低效果</t>
-  </si>
-  <si>
-    <t>死亡时触发释放复活</t>
-  </si>
-  <si>
-    <t>复活时回复血郞、触发间隔、每轮挑战最大次数</t>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放多重打击</t>
-  </si>
-  <si>
-    <t>提高多重打击的额外伤害</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放旋风斩</t>
-  </si>
-  <si>
-    <t>释放旋风斩触发释放半月斩</t>
-  </si>
-  <si>
-    <t>光环技能-自身效果：光环范围提高-范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
-  </si>
-  <si>
-    <t>攻击次数触发技能重击</t>
-  </si>
-  <si>
-    <t>重击技能暴击率提高</t>
-  </si>
-  <si>
-    <t>暴击触发技能：暴击伤害提高、重击需要的攻击次数累计值+1，致命暴击状态</t>
-  </si>
-  <si>
-    <t>技能攻击累计额外次数</t>
-  </si>
-  <si>
-    <t>致命暴击状态触发技能攻击速度提高</t>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-  </si>
-  <si>
-    <t>斩杀时暴击触发斩杀血线变化</t>
-  </si>
-  <si>
-    <t>斩杀血线的值增加</t>
-  </si>
-  <si>
-    <t>玩家1档普攻-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家2档普攻-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家3普攻-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物韧性被打空对自己释放易伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100201011,100201021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级1-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级2-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级4远程-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜘蛛怪等级1-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级2精英-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001011,1001021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002011,1002021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004011,1004021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14001011,14001021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3002011,3002021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11101,11102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11201,11202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12101,12102,12103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12201,12202,12203</t>
+  </si>
+  <si>
+    <t>13101,13102,13103</t>
+  </si>
+  <si>
+    <t>13201,13202,13203</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +554,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -549,7 +619,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -560,6 +630,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -841,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -902,7 +975,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>5010001</v>
+        <v>95100101</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -916,7 +989,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>5020001</v>
+        <v>95200101</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
@@ -930,41 +1003,41 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>5030001</v>
+        <v>95000101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>31000030</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>20010001</v>
+        <v>5030001</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>990102</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>20020001</v>
+        <v>20010001</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="C9" s="1">
+        <v>990102</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -972,13 +1045,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>20030001</v>
+        <v>20020001</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -986,13 +1059,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>20040001</v>
+        <v>20030001</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1000,13 +1073,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>20050001</v>
+        <v>20040001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -1014,13 +1087,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>20060001</v>
+        <v>20050001</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -1028,13 +1101,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>20070001</v>
+        <v>20060001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1042,13 +1115,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>20080001</v>
+        <v>20070001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -1056,13 +1129,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>20090001</v>
+        <v>20080001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1070,13 +1143,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>20100001</v>
+        <v>20090001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1084,13 +1157,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>20110001</v>
+        <v>20100001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1098,13 +1171,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>20120001</v>
+        <v>20110001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1112,13 +1185,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>20130001</v>
+        <v>20120001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1126,13 +1199,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>20140001</v>
+        <v>20130001</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1140,13 +1213,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>20150001</v>
+        <v>20140001</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1154,13 +1227,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>20160001</v>
+        <v>20150001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1168,111 +1241,111 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
+        <v>20160001</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
         <v>25010001</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>10102</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="2">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="A26" s="1">
+        <v>201001011</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>10201</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="A27" s="1">
+        <v>201002011</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>10202</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="2">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="A28" s="1">
+        <v>201004011</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>10301</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="A29" s="1">
+        <v>214001011</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>10302</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="A30" s="1">
+        <v>203002011</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>20001</v>
+        <v>10101</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1280,13 +1353,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>30001</v>
+        <v>10102</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="2">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1294,13 +1367,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>4000001</v>
+        <v>10201</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="2">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1308,192 +1381,192 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>5000001</v>
+        <v>10202</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="2">
-        <v>0</v>
+        <v>124</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="D34" s="2">
-        <v>31000010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>6000001</v>
+        <v>10301</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="D35" s="2">
-        <v>31000020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>6010001</v>
+        <v>10302</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="2">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D36" s="2">
-        <v>31000020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>7000001</v>
+        <v>20001</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
       </c>
       <c r="D37" s="2">
-        <v>31000040</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>7010001</v>
+        <v>30001</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>31000040</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>8000001</v>
+        <v>4000001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>31000030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>8010001</v>
+        <v>5000001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
       </c>
       <c r="D40" s="2">
-        <v>31000030</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>9000001</v>
+        <v>6000001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>0</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>10010001</v>
+        <v>6010001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
       <c r="D42" s="2">
-        <v>0</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>10020001</v>
+        <v>7000001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
       </c>
       <c r="D43" s="2">
-        <v>0</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>11010001</v>
+        <v>7010001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
       </c>
       <c r="D44" s="2">
-        <v>0</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>54010001</v>
+        <v>8000001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>54030001</v>
+        <v>8010001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
       </c>
       <c r="D46" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>54050001</v>
+        <v>9000001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1504,10 +1577,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>54070001</v>
+        <v>10010001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1518,10 +1591,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>54090001</v>
+        <v>10020001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1532,10 +1605,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>54110001</v>
+        <v>11010001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1546,10 +1619,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>54130001</v>
+        <v>54010001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1560,10 +1633,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>54150001</v>
+        <v>54030001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1574,10 +1647,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>54170001</v>
+        <v>54050001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1588,10 +1661,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>54190001</v>
+        <v>54070001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1602,10 +1675,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>54210001</v>
+        <v>54090001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1616,10 +1689,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>54230001</v>
+        <v>54110001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1630,10 +1703,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>54250001</v>
+        <v>54130001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1644,10 +1717,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>55010001</v>
+        <v>54150001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1658,10 +1731,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>55020001</v>
+        <v>54170001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1672,10 +1745,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>55030001</v>
+        <v>54190001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1686,10 +1759,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>55040001</v>
+        <v>54210001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1700,10 +1773,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>55050001</v>
+        <v>54230001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1714,10 +1787,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>55060001</v>
+        <v>54250001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1728,10 +1801,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>55070001</v>
+        <v>55010001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1742,10 +1815,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>56010001</v>
+        <v>55020001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1756,10 +1829,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>56040001</v>
+        <v>55030001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1770,10 +1843,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>56060001</v>
+        <v>55040001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1784,10 +1857,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>56080001</v>
+        <v>55050001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1798,10 +1871,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>56100001</v>
+        <v>55060001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1812,10 +1885,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>57010001</v>
+        <v>55070001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1826,10 +1899,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>57040001</v>
+        <v>56010001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1840,10 +1913,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>57060001</v>
+        <v>56040001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1854,10 +1927,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>57080001</v>
+        <v>56060001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1868,10 +1941,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>57100001</v>
+        <v>56080001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1882,10 +1955,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>57120001</v>
+        <v>56100001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1896,10 +1969,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>58010001</v>
+        <v>57010001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1910,10 +1983,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>58040001</v>
+        <v>57040001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1924,10 +1997,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>58060001</v>
+        <v>57060001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1938,10 +2011,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>58080001</v>
+        <v>57080001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1952,10 +2025,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>58110001</v>
+        <v>57100001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -1966,10 +2039,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>59010001</v>
+        <v>57120001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -1980,10 +2053,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>59030001</v>
+        <v>58010001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -1994,10 +2067,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>59050001</v>
+        <v>58040001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2008,10 +2081,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>59070001</v>
+        <v>58060001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2022,10 +2095,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>59090001</v>
+        <v>58080001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2036,10 +2109,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>59110001</v>
+        <v>58110001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2050,10 +2123,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>59130001</v>
+        <v>59010001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2064,10 +2137,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>59150001</v>
+        <v>59030001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2078,10 +2151,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>59180001</v>
+        <v>59050001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2092,10 +2165,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>59200001</v>
+        <v>59070001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2106,10 +2179,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>59220001</v>
+        <v>59090001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2120,10 +2193,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>60010001</v>
+        <v>59110001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2134,10 +2207,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>60030001</v>
+        <v>59130001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2148,10 +2221,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>60060001</v>
+        <v>59150001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2162,10 +2235,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>60090001</v>
+        <v>59180001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2176,10 +2249,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>60110001</v>
+        <v>59200001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2190,10 +2263,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>61020001</v>
+        <v>59220001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2204,10 +2277,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>61040001</v>
+        <v>60010001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2218,10 +2291,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>61060001</v>
+        <v>60030001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2232,10 +2305,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>61080001</v>
+        <v>60060001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2246,10 +2319,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>61100001</v>
+        <v>60090001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2260,10 +2333,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>61120001</v>
+        <v>60110001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2274,10 +2347,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>61140001</v>
+        <v>61020001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2288,10 +2361,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>61160001</v>
+        <v>61040001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2302,22 +2375,106 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
+        <v>61060001</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C105" s="2">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="2">
+        <v>61080001</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="2">
+        <v>61100001</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C107" s="2">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="2">
+        <v>61120001</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108" s="2">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="2">
+        <v>61140001</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="2">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="2">
+        <v>61160001</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110" s="2">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="2">
         <v>61180001</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C105" s="2">
-        <v>0</v>
-      </c>
-      <c r="D105" s="2">
+      <c r="B111" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D83" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:D30">
-    <sortCondition ref="A25:A30"/>
+  <autoFilter ref="A4:D89" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:D36">
+    <sortCondition ref="A31:A36"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
